--- a/data/education/working/fod_demo_soc.xlsx
+++ b/data/education/working/fod_demo_soc.xlsx
@@ -426,1351 +426,1289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>_Population 25 to 64 with a Bachelor's Degree or Higher4</t>
+          <t>Field of Degree</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>_64090000</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Male_46.3</t>
+          <t>Sex_Male</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Female_53.7</t>
+          <t>Sex_Female</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>25 to 34_28.1</t>
+          <t>Age_25 to 34</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>35 to 44_27.8</t>
+          <t>Age_35 to 44</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>45 to 54_23.5</t>
+          <t>Age_45 to 54</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>55 to 64_20.6</t>
+          <t>Age_55 to 64</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>White Alone_65.1</t>
+          <t>Race and Hispanic Origin2_White Alone</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Black Alone_8.7</t>
+          <t>Race and Hispanic Origin2_Black Alone</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Asian Alone_10.9</t>
+          <t>Race and Hispanic Origin2_Asian Alone</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Hispanic, of Any Race_10.6</t>
+          <t>Race and Hispanic Origin2_Hispanic, of Any Race</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Other or Multiple Race_4.7</t>
+          <t>Race and Hispanic Origin2_Other or Multiple Race</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Bachelor's Degree_62.1</t>
+          <t>Educational Attainmnent_Bachelor's Degree</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Master's Degree_27.6</t>
+          <t>Educational Attainmnent_Master's Degree</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Professional Degree_6</t>
+          <t>Educational Attainmnent_Professional Degree</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Doctorate Degree_4.4</t>
+          <t>Educational Attainmnent_Doctorate Degree</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Employed_85.8</t>
+          <t>Employment_Employed</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Unemployed_1.9</t>
+          <t>Employment_Unemployed</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Not in Labor Force_12.3</t>
+          <t>Employment_Not in Labor Force</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>In Poverty_4.2</t>
+          <t>Poverty Status_In Poverty</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Not in Poverty_95.8</t>
+          <t>Poverty Status_Not in Poverty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Field of Degree</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Age </t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Race and Hispanic Origin2 </t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Educational Attainmnent </t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Poverty Status </t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr"/>
+          <t>Population 25 to 64 with a Bachelor's Degree or Higher4</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>64090000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>95.8</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science and Engineering Degrees </t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Male </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Female </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>25 to 34</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35 to 44 </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45 to 54 </t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>55 to 64</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>White Alone</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Black Alone</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Asian Alone</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hispanic, of Any Race </t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other or Multiple Race </t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bachelor's Degree </t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Master's Degree </t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Professional Degree </t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Doctorate Degree </t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Employed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unemployed </t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not in Labor Force </t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In Poverty </t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not in Poverty </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Population 25 to 64 with a Bachelor's Degree or Higher4</t>
+          <t xml:space="preserve">Computer Science </t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64090000</v>
+        <v>1665000</v>
       </c>
       <c r="C4" t="n">
-        <v>46.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>53.7</v>
+        <v>24.9</v>
       </c>
       <c r="E4" t="n">
-        <v>28.1</v>
+        <v>30.9</v>
       </c>
       <c r="F4" t="n">
-        <v>27.8</v>
+        <v>29.5</v>
       </c>
       <c r="G4" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="H4" t="n">
-        <v>20.6</v>
+        <v>18.1</v>
       </c>
       <c r="I4" t="n">
-        <v>65.09999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="J4" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="n">
-        <v>10.9</v>
+        <v>29.3</v>
       </c>
       <c r="L4" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="M4" t="n">
         <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>62.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>85.8</v>
+        <v>88.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="V4" t="n">
-        <v>95.8</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science and Engineering Degrees </t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+          <t xml:space="preserve">Engineering </t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>695400</v>
+      </c>
+      <c r="C5" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>61</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>95.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer Science </t>
+          <t xml:space="preserve">Civil Engineering </t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1665000</v>
+        <v>556200</v>
       </c>
       <c r="C6" t="n">
-        <v>75.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="D6" t="n">
-        <v>24.9</v>
+        <v>22.3</v>
       </c>
       <c r="E6" t="n">
-        <v>30.9</v>
+        <v>29.7</v>
       </c>
       <c r="F6" t="n">
-        <v>29.5</v>
+        <v>25.8</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="H6" t="n">
-        <v>18.1</v>
+        <v>22.1</v>
       </c>
       <c r="I6" t="n">
-        <v>49.6</v>
+        <v>62.1</v>
       </c>
       <c r="J6" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>29.3</v>
+        <v>16.4</v>
       </c>
       <c r="L6" t="n">
-        <v>8.6</v>
+        <v>12.3</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>67.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="O6" t="n">
-        <v>28.1</v>
+        <v>29.7</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>88.2</v>
+        <v>89.8</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V6" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engineering </t>
+          <t xml:space="preserve">Electrical Engineering </t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>695400</v>
+        <v>1197000</v>
       </c>
       <c r="C7" t="n">
-        <v>81.3</v>
+        <v>84.5</v>
       </c>
       <c r="D7" t="n">
-        <v>18.7</v>
+        <v>15.5</v>
       </c>
       <c r="E7" t="n">
-        <v>24.1</v>
+        <v>22.5</v>
       </c>
       <c r="F7" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="G7" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.4</v>
+        <v>27.5</v>
       </c>
       <c r="I7" t="n">
-        <v>53.9</v>
+        <v>47.1</v>
       </c>
       <c r="J7" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="K7" t="n">
-        <v>20.2</v>
+        <v>33.6</v>
       </c>
       <c r="L7" t="n">
-        <v>14.2</v>
+        <v>9.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>61</v>
+        <v>53.2</v>
       </c>
       <c r="O7" t="n">
-        <v>31.3</v>
+        <v>37.2</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="R7" t="n">
-        <v>87.8</v>
+        <v>88.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="T7" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Engineering </t>
+          <t xml:space="preserve">Mechanical Engineering </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>556200</v>
+        <v>1033000</v>
       </c>
       <c r="C8" t="n">
-        <v>77.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>22.3</v>
+        <v>11.9</v>
       </c>
       <c r="E8" t="n">
-        <v>29.7</v>
+        <v>33.4</v>
       </c>
       <c r="F8" t="n">
-        <v>25.8</v>
+        <v>23.7</v>
       </c>
       <c r="G8" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="I8" t="n">
-        <v>62.1</v>
+        <v>64.8</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>16.4</v>
+        <v>18.2</v>
       </c>
       <c r="L8" t="n">
-        <v>12.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>63.9</v>
+        <v>61.2</v>
       </c>
       <c r="O8" t="n">
-        <v>29.7</v>
+        <v>31.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>89.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical Engineering </t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1197000</v>
+        <v>699900</v>
       </c>
       <c r="C9" t="n">
-        <v>84.5</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>15.5</v>
+        <v>43</v>
       </c>
       <c r="E9" t="n">
-        <v>22.5</v>
+        <v>27.2</v>
       </c>
       <c r="F9" t="n">
-        <v>26.3</v>
+        <v>24.5</v>
       </c>
       <c r="G9" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="H9" t="n">
-        <v>27.5</v>
+        <v>25.4</v>
       </c>
       <c r="I9" t="n">
-        <v>47.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>33.6</v>
+        <v>15.3</v>
       </c>
       <c r="L9" t="n">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>53.2</v>
+        <v>48.5</v>
       </c>
       <c r="O9" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="R9" t="n">
-        <v>88.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S9" t="n">
         <v>1.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="V9" t="n">
-        <v>96.5</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical Engineering </t>
+          <t xml:space="preserve">Biology </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1033000</v>
+        <v>2201000</v>
       </c>
       <c r="C10" t="n">
-        <v>88.09999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="D10" t="n">
-        <v>11.9</v>
+        <v>55.8</v>
       </c>
       <c r="E10" t="n">
-        <v>33.4</v>
+        <v>35.6</v>
       </c>
       <c r="F10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>63</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="O10" t="n">
         <v>23.7</v>
       </c>
-      <c r="G10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>31.8</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>12.9</v>
       </c>
       <c r="R10" t="n">
-        <v>90.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="S10" t="n">
         <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>11.3</v>
       </c>
       <c r="U10" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="V10" t="n">
-        <v>96.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t xml:space="preserve">Chemistry </t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>699900</v>
+        <v>613000</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="E11" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="F11" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G11" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="H11" t="n">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
       <c r="I11" t="n">
-        <v>65.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="J11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="K11" t="n">
-        <v>15.3</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>48.5</v>
+        <v>37.1</v>
       </c>
       <c r="O11" t="n">
-        <v>38.6</v>
+        <v>25.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.1</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
-        <v>85.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T11" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="U11" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="V11" t="n">
-        <v>95.8</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biology </t>
+          <t xml:space="preserve">Psychology </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2201000</v>
+        <v>3075000</v>
       </c>
       <c r="C12" t="n">
-        <v>44.2</v>
+        <v>26.3</v>
       </c>
       <c r="D12" t="n">
-        <v>55.8</v>
+        <v>73.7</v>
       </c>
       <c r="E12" t="n">
-        <v>35.6</v>
+        <v>32.6</v>
       </c>
       <c r="F12" t="n">
-        <v>26.6</v>
+        <v>28.9</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="H12" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="I12" t="n">
-        <v>63</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>6.3</v>
       </c>
       <c r="L12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="M12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.4</v>
-      </c>
       <c r="V12" t="n">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry </t>
+          <t xml:space="preserve">Economics </t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>613000</v>
+        <v>1267000</v>
       </c>
       <c r="C13" t="n">
-        <v>56.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>43.1</v>
+        <v>35.1</v>
       </c>
       <c r="E13" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>24.9</v>
+        <v>26.1</v>
       </c>
       <c r="G13" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="H13" t="n">
-        <v>24.7</v>
+        <v>23.9</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>62.2</v>
       </c>
       <c r="J13" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>17.4</v>
       </c>
       <c r="L13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>37.1</v>
+        <v>58.6</v>
       </c>
       <c r="O13" t="n">
-        <v>25.2</v>
+        <v>29.1</v>
       </c>
       <c r="P13" t="n">
-        <v>15.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>86.8</v>
+        <v>85.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="U13" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="V13" t="n">
-        <v>96.3</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychology </t>
+          <t xml:space="preserve">Political Science </t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3075000</v>
+        <v>1440000</v>
       </c>
       <c r="C14" t="n">
-        <v>26.3</v>
+        <v>56.8</v>
       </c>
       <c r="D14" t="n">
-        <v>73.7</v>
+        <v>43.2</v>
       </c>
       <c r="E14" t="n">
-        <v>32.6</v>
+        <v>26.6</v>
       </c>
       <c r="F14" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="G14" t="n">
-        <v>23.3</v>
+        <v>25.1</v>
       </c>
       <c r="H14" t="n">
-        <v>15.1</v>
+        <v>20.2</v>
       </c>
       <c r="I14" t="n">
-        <v>65.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="L14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>52.4</v>
+        <v>47.5</v>
       </c>
       <c r="O14" t="n">
-        <v>34.5</v>
+        <v>26.4</v>
       </c>
       <c r="P14" t="n">
-        <v>6.3</v>
+        <v>21.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>84.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="V14" t="n">
-        <v>95</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Economics </t>
+          <t xml:space="preserve">Sociology </t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1267000</v>
+        <v>878800</v>
       </c>
       <c r="C15" t="n">
-        <v>64.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="D15" t="n">
-        <v>35.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="F15" t="n">
-        <v>26.1</v>
+        <v>29.5</v>
       </c>
       <c r="G15" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.9</v>
+        <v>17.9</v>
       </c>
       <c r="I15" t="n">
-        <v>62.2</v>
+        <v>59.1</v>
       </c>
       <c r="J15" t="n">
-        <v>6.6</v>
+        <v>14.9</v>
       </c>
       <c r="K15" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="N15" t="n">
-        <v>58.6</v>
+        <v>62.9</v>
       </c>
       <c r="O15" t="n">
-        <v>29.1</v>
+        <v>28.1</v>
       </c>
       <c r="P15" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>85.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="U15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Political Science </t>
+          <t xml:space="preserve">Nursing </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1440000</v>
+        <v>2842000</v>
       </c>
       <c r="C16" t="n">
-        <v>56.8</v>
+        <v>12.1</v>
       </c>
       <c r="D16" t="n">
-        <v>43.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>26.6</v>
+        <v>28.4</v>
       </c>
       <c r="F16" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="G16" t="n">
-        <v>25.1</v>
+        <v>23.4</v>
       </c>
       <c r="H16" t="n">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="I16" t="n">
-        <v>69.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="J16" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="K16" t="n">
-        <v>6.9</v>
+        <v>12.4</v>
       </c>
       <c r="L16" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>47.5</v>
+        <v>71.2</v>
       </c>
       <c r="O16" t="n">
-        <v>26.4</v>
+        <v>20.9</v>
       </c>
       <c r="P16" t="n">
-        <v>21.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>87.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="U16" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="V16" t="n">
-        <v>95.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sociology </t>
+          <t>Other Science and Engineering Degrees3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>878800</v>
+        <v>11870000</v>
       </c>
       <c r="C17" t="n">
-        <v>31.4</v>
+        <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>68.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>26.9</v>
+        <v>32.3</v>
       </c>
       <c r="F17" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="G17" t="n">
-        <v>25.8</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="I17" t="n">
-        <v>59.1</v>
+        <v>62.2</v>
       </c>
       <c r="J17" t="n">
-        <v>14.9</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>7.4</v>
+        <v>14.3</v>
       </c>
       <c r="L17" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="M17" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>62.9</v>
+        <v>56.3</v>
       </c>
       <c r="O17" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
       <c r="P17" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="R17" t="n">
-        <v>83.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="T17" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="V17" t="n">
-        <v>95.40000000000001</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nursing </t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2842000</v>
-      </c>
-      <c r="C18" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>96.90000000000001</v>
-      </c>
+          <t xml:space="preserve">Business Degrees </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other Science and Engineering Degrees3</t>
+          <t xml:space="preserve">General Business </t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11870000</v>
+        <v>2844000</v>
       </c>
       <c r="C19" t="n">
-        <v>51</v>
+        <v>57.2</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>42.8</v>
       </c>
       <c r="E19" t="n">
-        <v>32.3</v>
+        <v>21.1</v>
       </c>
       <c r="F19" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="H19" t="n">
-        <v>18.3</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>62.2</v>
+        <v>67</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>14.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>56.3</v>
+        <v>74.7</v>
       </c>
       <c r="O19" t="n">
-        <v>29.1</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="R19" t="n">
-        <v>86.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T19" t="n">
-        <v>11.4</v>
+        <v>13.5</v>
       </c>
       <c r="U19" t="n">
         <v>4.2</v>
@@ -1782,93 +1720,135 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Degrees </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+          <t xml:space="preserve">Accounting </t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2290000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>96.40000000000001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Business </t>
+          <t xml:space="preserve">Business Management and Adminstration </t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2844000</v>
+        <v>3839000</v>
       </c>
       <c r="C21" t="n">
-        <v>57.2</v>
+        <v>51.3</v>
       </c>
       <c r="D21" t="n">
-        <v>42.8</v>
+        <v>48.7</v>
       </c>
       <c r="E21" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="F21" t="n">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="I21" t="n">
-        <v>67</v>
+        <v>62.1</v>
       </c>
       <c r="J21" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="K21" t="n">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L21" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="M21" t="n">
         <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="O21" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
         <v>1.2</v>
       </c>
       <c r="R21" t="n">
-        <v>84.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="U21" t="n">
         <v>4.2</v>
@@ -1880,1393 +1860,1309 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounting </t>
+          <t xml:space="preserve">Marketing </t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2290000</v>
+        <v>1516000</v>
       </c>
       <c r="C22" t="n">
-        <v>45.3</v>
+        <v>42.8</v>
       </c>
       <c r="D22" t="n">
-        <v>54.7</v>
+        <v>57.2</v>
       </c>
       <c r="E22" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="F22" t="n">
-        <v>24.6</v>
+        <v>28.7</v>
       </c>
       <c r="G22" t="n">
-        <v>25.7</v>
+        <v>22.5</v>
       </c>
       <c r="H22" t="n">
-        <v>27.3</v>
+        <v>20.2</v>
       </c>
       <c r="I22" t="n">
-        <v>62.7</v>
+        <v>71.7</v>
       </c>
       <c r="J22" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>68.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>26.5</v>
+        <v>15.2</v>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="R22" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="U22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V22" t="n">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Management and Adminstration </t>
+          <t xml:space="preserve">Finance </t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3839000</v>
+        <v>1429000</v>
       </c>
       <c r="C23" t="n">
-        <v>51.3</v>
+        <v>65.5</v>
       </c>
       <c r="D23" t="n">
-        <v>48.7</v>
+        <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>20.8</v>
+        <v>29.8</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>28.6</v>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>22.4</v>
       </c>
       <c r="H23" t="n">
-        <v>26.2</v>
+        <v>19.2</v>
       </c>
       <c r="I23" t="n">
-        <v>62.1</v>
+        <v>68.5</v>
       </c>
       <c r="J23" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
-        <v>13.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>75.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>20.9</v>
+        <v>24.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>86.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T23" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="V23" t="n">
-        <v>95.8</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marketing </t>
+          <t xml:space="preserve">Other Business Degrees </t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1516000</v>
+        <v>1615000</v>
       </c>
       <c r="C24" t="n">
-        <v>42.8</v>
+        <v>49.1</v>
       </c>
       <c r="D24" t="n">
-        <v>57.2</v>
+        <v>50.9</v>
       </c>
       <c r="E24" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="F24" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="G24" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H24" t="n">
-        <v>20.2</v>
+        <v>16.9</v>
       </c>
       <c r="I24" t="n">
-        <v>71.7</v>
+        <v>60.7</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>11.7</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>13.1</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>82.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>15.2</v>
+        <v>20.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="R24" t="n">
-        <v>85.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="V24" t="n">
-        <v>96.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance </t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1429000</v>
-      </c>
-      <c r="C25" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G25" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>11</v>
-      </c>
-      <c r="L25" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="O25" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>96.8</v>
-      </c>
+          <t xml:space="preserve">Education Degrees </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Business Degrees </t>
+          <t>General Education</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1615000</v>
+        <v>1876000</v>
       </c>
       <c r="C26" t="n">
-        <v>49.1</v>
+        <v>22.4</v>
       </c>
       <c r="D26" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28</v>
+      </c>
+      <c r="H26" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N26" t="n">
         <v>50.9</v>
       </c>
-      <c r="E26" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L26" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N26" t="n">
-        <v>75.40000000000001</v>
-      </c>
       <c r="O26" t="n">
-        <v>20.9</v>
+        <v>42.9</v>
       </c>
       <c r="P26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="R26" t="n">
-        <v>87.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>10.9</v>
+        <v>17.8</v>
       </c>
       <c r="U26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="V26" t="n">
-        <v>95.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Degrees </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+          <t>Elementary Education</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1491000</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>96.90000000000001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>General Education</t>
+          <t>Other Education Degrees</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1876000</v>
+        <v>2032000</v>
       </c>
       <c r="C28" t="n">
-        <v>22.4</v>
+        <v>29.3</v>
       </c>
       <c r="D28" t="n">
-        <v>77.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="E28" t="n">
-        <v>18.3</v>
+        <v>21.9</v>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="G28" t="n">
-        <v>28</v>
+        <v>24.2</v>
       </c>
       <c r="H28" t="n">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
       <c r="I28" t="n">
-        <v>68.2</v>
+        <v>76.5</v>
       </c>
       <c r="J28" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="K28" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>50.9</v>
+        <v>49.3</v>
       </c>
       <c r="O28" t="n">
-        <v>42.9</v>
+        <v>43.8</v>
       </c>
       <c r="P28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>81</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T28" t="n">
-        <v>17.8</v>
+        <v>15.8</v>
       </c>
       <c r="U28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V28" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Elementary Education</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1491000</v>
-      </c>
-      <c r="C29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N29" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>96.90000000000001</v>
-      </c>
+          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other Education Degrees</t>
+          <t xml:space="preserve">Communications </t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2032000</v>
+        <v>1658000</v>
       </c>
       <c r="C30" t="n">
-        <v>29.3</v>
+        <v>38.2</v>
       </c>
       <c r="D30" t="n">
-        <v>70.7</v>
+        <v>61.8</v>
       </c>
       <c r="E30" t="n">
-        <v>21.9</v>
+        <v>30.1</v>
       </c>
       <c r="F30" t="n">
-        <v>26.8</v>
+        <v>30.5</v>
       </c>
       <c r="G30" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="H30" t="n">
-        <v>27.2</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>76.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="L30" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>49.3</v>
+        <v>76</v>
       </c>
       <c r="O30" t="n">
-        <v>43.8</v>
+        <v>19</v>
       </c>
       <c r="P30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="U30" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V30" t="n">
-        <v>96.5</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+          <t xml:space="preserve">English Language and Literature </t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1670000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>53</v>
+      </c>
+      <c r="O31" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>95.2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communications </t>
+          <t xml:space="preserve">Liberal Arts </t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1658000</v>
+        <v>744600</v>
       </c>
       <c r="C32" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="D32" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="E32" t="n">
-        <v>30.1</v>
+        <v>21.5</v>
       </c>
       <c r="F32" t="n">
-        <v>30.5</v>
+        <v>29.1</v>
       </c>
       <c r="G32" t="n">
-        <v>23.4</v>
+        <v>26.2</v>
       </c>
       <c r="H32" t="n">
-        <v>16</v>
+        <v>23.2</v>
       </c>
       <c r="I32" t="n">
-        <v>70.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>76</v>
+        <v>71.8</v>
       </c>
       <c r="O32" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="P32" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>86.3</v>
+        <v>81.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>11.4</v>
+        <v>16.1</v>
       </c>
       <c r="U32" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="V32" t="n">
-        <v>96.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">English Language and Literature </t>
+          <t xml:space="preserve">History </t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1670000</v>
+        <v>1166000</v>
       </c>
       <c r="C33" t="n">
-        <v>33.6</v>
+        <v>60.8</v>
       </c>
       <c r="D33" t="n">
-        <v>66.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="E33" t="n">
         <v>23.3</v>
       </c>
       <c r="F33" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="G33" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="H33" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="I33" t="n">
-        <v>72.8</v>
+        <v>77.2</v>
       </c>
       <c r="J33" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="L33" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M33" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>53</v>
+        <v>49.6</v>
       </c>
       <c r="O33" t="n">
-        <v>32.7</v>
+        <v>31.4</v>
       </c>
       <c r="P33" t="n">
-        <v>8.800000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>83.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T33" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="U33" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="V33" t="n">
-        <v>95.2</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liberal Arts </t>
+          <t xml:space="preserve">Fine Arts </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>744600</v>
+        <v>684600</v>
       </c>
       <c r="C34" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="D34" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="E34" t="n">
-        <v>21.5</v>
+        <v>23.4</v>
       </c>
       <c r="F34" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="G34" t="n">
-        <v>26.2</v>
+        <v>25.4</v>
       </c>
       <c r="H34" t="n">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="I34" t="n">
-        <v>65.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>9.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="K34" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="L34" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="N34" t="n">
-        <v>71.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="P34" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
-        <v>81.3</v>
+        <v>80.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="U34" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="V34" t="n">
-        <v>93.59999999999999</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">History </t>
+          <t xml:space="preserve">Commerical Art and Graphic Design </t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1166000</v>
+        <v>723300</v>
       </c>
       <c r="C35" t="n">
-        <v>60.8</v>
+        <v>34.2</v>
       </c>
       <c r="D35" t="n">
-        <v>39.2</v>
+        <v>65.8</v>
       </c>
       <c r="E35" t="n">
-        <v>23.3</v>
+        <v>32.5</v>
       </c>
       <c r="F35" t="n">
-        <v>29.5</v>
+        <v>32.1</v>
       </c>
       <c r="G35" t="n">
-        <v>26.6</v>
+        <v>19.8</v>
       </c>
       <c r="H35" t="n">
-        <v>20.6</v>
+        <v>15.6</v>
       </c>
       <c r="I35" t="n">
-        <v>77.2</v>
+        <v>66</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="L35" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N35" t="n">
-        <v>49.6</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>31.4</v>
+        <v>10.1</v>
       </c>
       <c r="P35" t="n">
-        <v>13.9</v>
+        <v>1.1</v>
       </c>
       <c r="Q35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>14</v>
+      </c>
+      <c r="U35" t="n">
         <v>5</v>
       </c>
-      <c r="R35" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.9</v>
-      </c>
       <c r="V35" t="n">
-        <v>96.09999999999999</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fine Arts </t>
+          <t xml:space="preserve">Family and Consumer Sciences </t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>684600</v>
+        <v>493300</v>
       </c>
       <c r="C36" t="n">
-        <v>38.3</v>
+        <v>9.5</v>
       </c>
       <c r="D36" t="n">
-        <v>61.7</v>
+        <v>90.5</v>
       </c>
       <c r="E36" t="n">
-        <v>23.4</v>
+        <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>29.6</v>
+        <v>27.9</v>
       </c>
       <c r="G36" t="n">
-        <v>25.4</v>
+        <v>22.1</v>
       </c>
       <c r="H36" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="I36" t="n">
-        <v>69.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="J36" t="n">
-        <v>6.1</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="L36" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="M36" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>76.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="O36" t="n">
-        <v>19.6</v>
+        <v>26.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>80.8</v>
+        <v>80.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="T36" t="n">
-        <v>16.3</v>
+        <v>18</v>
       </c>
       <c r="U36" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="V36" t="n">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commerical Art and Graphic Design </t>
+          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>723300</v>
+        <v>855900</v>
       </c>
       <c r="C37" t="n">
-        <v>34.2</v>
+        <v>54.7</v>
       </c>
       <c r="D37" t="n">
-        <v>65.8</v>
+        <v>45.3</v>
       </c>
       <c r="E37" t="n">
-        <v>32.5</v>
+        <v>47.9</v>
       </c>
       <c r="F37" t="n">
-        <v>32.1</v>
+        <v>27.3</v>
       </c>
       <c r="G37" t="n">
-        <v>19.8</v>
+        <v>17.3</v>
       </c>
       <c r="H37" t="n">
-        <v>15.6</v>
+        <v>7.5</v>
       </c>
       <c r="I37" t="n">
-        <v>66</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>5.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>88.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>10.1</v>
+        <v>22.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="R37" t="n">
-        <v>83.2</v>
+        <v>88.5</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="T37" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family and Consumer Sciences </t>
+          <t>Criminal Justice and Fire Protection</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>493300</v>
+        <v>1385000</v>
       </c>
       <c r="C38" t="n">
-        <v>9.5</v>
+        <v>58.2</v>
       </c>
       <c r="D38" t="n">
-        <v>90.5</v>
+        <v>41.8</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="F38" t="n">
-        <v>27.9</v>
+        <v>29.2</v>
       </c>
       <c r="G38" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="H38" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I38" t="n">
-        <v>67.7</v>
+        <v>61.3</v>
       </c>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>15.9</v>
       </c>
       <c r="K38" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="L38" t="n">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>68.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>26.5</v>
+        <v>18.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="R38" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.7</v>
-      </c>
       <c r="T38" t="n">
-        <v>18</v>
+        <v>10.3</v>
       </c>
       <c r="U38" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="V38" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
+          <t xml:space="preserve">Social Work </t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>855900</v>
+        <v>637700</v>
       </c>
       <c r="C39" t="n">
-        <v>54.7</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>45.3</v>
+        <v>87</v>
       </c>
       <c r="E39" t="n">
-        <v>47.9</v>
+        <v>27.8</v>
       </c>
       <c r="F39" t="n">
         <v>27.3</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3</v>
+        <v>25.2</v>
       </c>
       <c r="H39" t="n">
-        <v>7.5</v>
+        <v>19.8</v>
       </c>
       <c r="I39" t="n">
-        <v>72.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="J39" t="n">
-        <v>8.300000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="K39" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>65.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="O39" t="n">
-        <v>22.6</v>
+        <v>47.1</v>
       </c>
       <c r="P39" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>88.5</v>
+        <v>83.3</v>
       </c>
       <c r="S39" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="T39" t="n">
-        <v>9.6</v>
+        <v>15.1</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="V39" t="n">
-        <v>96</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Criminal Justice and Fire Protection</t>
+          <t xml:space="preserve">Other Degrees </t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1385000</v>
+        <v>5103000</v>
       </c>
       <c r="C40" t="n">
-        <v>58.2</v>
+        <v>47.2</v>
       </c>
       <c r="D40" t="n">
-        <v>41.8</v>
+        <v>52.8</v>
       </c>
       <c r="E40" t="n">
-        <v>32.1</v>
+        <v>30.3</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="G40" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="H40" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="I40" t="n">
-        <v>61.3</v>
+        <v>69</v>
       </c>
       <c r="J40" t="n">
-        <v>15.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="L40" t="n">
-        <v>15.2</v>
+        <v>10.5</v>
       </c>
       <c r="M40" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="N40" t="n">
-        <v>76.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>18.1</v>
+        <v>25.1</v>
       </c>
       <c r="P40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" t="n">
-        <v>1.4</v>
-      </c>
       <c r="R40" t="n">
-        <v>87.7</v>
+        <v>84.8</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T40" t="n">
-        <v>10.3</v>
+        <v>12.8</v>
       </c>
       <c r="U40" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="V40" t="n">
-        <v>95.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Social Work </t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>637700</v>
-      </c>
-      <c r="C41" t="n">
-        <v>13</v>
-      </c>
-      <c r="D41" t="n">
-        <v>87</v>
-      </c>
-      <c r="E41" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="J41" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N41" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="O41" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V41" t="n">
-        <v>94.7</v>
-      </c>
+          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Degrees </t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>5103000</v>
-      </c>
-      <c r="C42" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G42" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="I42" t="n">
-        <v>69</v>
-      </c>
-      <c r="J42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="O42" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>94.59999999999999</v>
-      </c>
+          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+          <t>Note: 1. See margins of error for these estimates in Table M1. 2. Race groups are non-Hispanic unless otherwise noted. 3. Science and Engineering related fields are included within the "other science and engineering degrees" category. 4.  We are unable to determine what field respondents pursue an advanced degree in. The field of degree question on the American Community Survey asks about Bachelor's degree.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -3291,62 +3187,6 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Note: 1. See margins of error for these estimates in Table M1. 2. Race groups are non-Hispanic unless otherwise noted. 3. Science and Engineering related fields are included within the "other science and engineering degrees" category. 4.  We are unable to determine what field respondents pursue an advanced degree in. The field of degree question on the American Community Survey asks about Bachelor's degree.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3358,2847 +3198,2743 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>_Population 25 to 64 with a Bachelor's Degree or Higher</t>
+          <t>Field of Degree</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>_232300</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Male_0.08</t>
+          <t>Sex_Male</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Female_0.08</t>
+          <t>Sex_Female</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>25 to 34_0.09</t>
+          <t>Age_25 to 34</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>35 to 44_0.08</t>
+          <t>Age_35 to 44</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>45 to 54_0.07</t>
+          <t>Age_45 to 54</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>55 to 64_0.07</t>
+          <t>Age_55 to 64</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>White Alone_0.1</t>
+          <t>Race and Hispanic Origin_White Alone</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Black Alone_0.07</t>
+          <t>Race and Hispanic Origin_Black Alone</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Asian Alone_0.05</t>
+          <t>Race and Hispanic Origin_Asian Alone</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Hispanic, of Any Race_0.07</t>
+          <t>Race and Hispanic Origin_Hispanic, of Any Race</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Other or Multiple Race_0.05</t>
+          <t>Race and Hispanic Origin_Other or Multiple Race</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Bachelor's Degree_0.11</t>
+          <t>Educational Attainmnent_Bachelor's Degree</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Master's Degree_0.1</t>
+          <t>Educational Attainmnent_Master's Degree</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Professional Degree_0.06</t>
+          <t>Educational Attainmnent_Professional Degree</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Doctorate Degree_0.04</t>
+          <t>Educational Attainmnent_Doctorate Degree</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Employed_0.07</t>
+          <t>Employment_Employed</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Unemployed_0.03</t>
+          <t>Employment_Unemployed</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Not in Labor Force_0.07</t>
+          <t>Employment_Not in Labor Force</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>In Poverty_0.05</t>
+          <t>Poverty Status_In Poverty</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Not In Poverty_0.05</t>
+          <t>Poverty Status_Not In Poverty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Field of Degree</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Age </t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Race and Hispanic Origin </t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Educational Attainmnent </t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Poverty Status </t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr"/>
+          <t xml:space="preserve">Population 25 to 64 with a Bachelor's Degree or Higher </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>232300</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science and Engineering Degrees </t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Male </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Female </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>25 to 34</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35 to 44 </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45 to 54 </t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>55 to 64</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>White Alone</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Black Alone</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Asian Alone</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hispanic, of Any Race </t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other or Multiple Race </t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bachelor's Degree </t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Master's Degree </t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Professional Degree </t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Doctorate Degree </t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Employed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unemployed </t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not in Labor Force </t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In Poverty </t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not In Poverty </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Population 25 to 64 with a Bachelor's Degree or Higher </t>
+          <t xml:space="preserve">Computer Science </t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232300</v>
+        <v>23960</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.67</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.68</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="N4" t="n">
-        <v>0.11</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1</v>
+        <v>0.64</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science and Engineering Degrees </t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+          <t xml:space="preserve">Engineering </t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18560</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer Science </t>
+          <t xml:space="preserve">Civil Engineering </t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23960</v>
+        <v>14310</v>
       </c>
       <c r="C6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.59</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="K6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.73</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>0.32</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.17</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="U6" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engineering </t>
+          <t xml:space="preserve">Electrical Engineering </t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18560</v>
+        <v>22550</v>
       </c>
       <c r="C7" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="J7" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="K7" t="n">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="L7" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="N7" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="P7" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="R7" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="T7" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="U7" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Engineering </t>
+          <t xml:space="preserve">Mechanical Engineering </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14310</v>
+        <v>20030</v>
       </c>
       <c r="C8" t="n">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="D8" t="n">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="E8" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
       <c r="G8" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.59</v>
+        <v>0.39</v>
       </c>
       <c r="K8" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="L8" t="n">
-        <v>0.85</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.52</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.73</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical Engineering </t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22550</v>
+        <v>15290</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E9" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="F9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.71</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>0.28</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.24</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="U9" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical Engineering </t>
+          <t xml:space="preserve">Biology </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20030</v>
+        <v>27830</v>
       </c>
       <c r="C10" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="F10" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="G10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.66</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="K10" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="L10" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.41</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T10" t="n">
         <v>0.4</v>
       </c>
-      <c r="R10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.51</v>
-      </c>
       <c r="U10" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t xml:space="preserve">Chemistry </t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15290</v>
+        <v>13330</v>
       </c>
       <c r="C11" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="D11" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="E11" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="F11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.01</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.84</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="K11" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="N11" t="n">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="O11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.39</v>
+        <v>0.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="R11" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="S11" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="V11" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biology </t>
+          <t xml:space="preserve">Psychology </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27830</v>
+        <v>36010</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="F12" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="J12" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="K12" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="L12" t="n">
         <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="P12" t="n">
-        <v>0.51</v>
+        <v>0.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="V12" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry </t>
+          <t xml:space="preserve">Economics </t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13330</v>
+        <v>19010</v>
       </c>
       <c r="C13" t="n">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="n">
-        <v>1.04</v>
+        <v>0.78</v>
       </c>
       <c r="F13" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="G13" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="J13" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="N13" t="n">
-        <v>1.19</v>
+        <v>0.87</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.82</v>
+        <v>0.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="S13" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="T13" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychology </t>
+          <t xml:space="preserve">Political Science </t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36010</v>
+        <v>22890</v>
       </c>
       <c r="C14" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="E14" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="F14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.4</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="S14" t="n">
         <v>0.26</v>
       </c>
-      <c r="N14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.13</v>
-      </c>
       <c r="T14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="U14" t="n">
         <v>0.33</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.24</v>
-      </c>
       <c r="V14" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Economics </t>
+          <t xml:space="preserve">Sociology </t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19010</v>
+        <v>17350</v>
       </c>
       <c r="C15" t="n">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="G15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.67</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.7</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="J15" t="n">
-        <v>0.48</v>
+        <v>0.79</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="N15" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="R15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="T15" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="U15" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="V15" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Political Science </t>
+          <t xml:space="preserve">Nursing </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22890</v>
+        <v>32200</v>
       </c>
       <c r="C16" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="D16" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="E16" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="F16" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="G16" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H16" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="J16" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="K16" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="L16" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="N16" t="n">
-        <v>0.78</v>
+        <v>0.49</v>
       </c>
       <c r="O16" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="P16" t="n">
-        <v>0.66</v>
+        <v>0.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="U16" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="V16" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sociology </t>
+          <t>Other Science and Engineering Degrees1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17350</v>
+        <v>71600</v>
       </c>
       <c r="C17" t="n">
-        <v>0.93</v>
+        <v>0.23</v>
       </c>
       <c r="D17" t="n">
-        <v>0.93</v>
+        <v>0.23</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
-        <v>0.86</v>
+        <v>0.23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.83</v>
+        <v>0.19</v>
       </c>
       <c r="H17" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.92</v>
+        <v>0.25</v>
       </c>
       <c r="J17" t="n">
-        <v>0.79</v>
+        <v>0.17</v>
       </c>
       <c r="K17" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="L17" t="n">
-        <v>0.61</v>
+        <v>0.18</v>
       </c>
       <c r="M17" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.84</v>
+        <v>0.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0.84</v>
+        <v>0.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="R17" t="n">
-        <v>0.62</v>
+        <v>0.16</v>
       </c>
       <c r="S17" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0.63</v>
+        <v>0.16</v>
       </c>
       <c r="U17" t="n">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
       <c r="V17" t="n">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nursing </t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>32200</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.19</v>
-      </c>
+          <t xml:space="preserve">Business Degrees </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other Science and Engineering Degrees1</t>
+          <t xml:space="preserve">General Business </t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71600</v>
+        <v>33340</v>
       </c>
       <c r="C19" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="D19" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="E19" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="F19" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
       <c r="G19" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="H19" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="I19" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J19" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P19" t="n">
         <v>0.17</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.13</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.05</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Degrees </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+          <t xml:space="preserve">Accounting </t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>27970</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Business </t>
+          <t xml:space="preserve">Business Management and Adminstration </t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33340</v>
+        <v>39440</v>
       </c>
       <c r="C21" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="D21" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="E21" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="F21" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="G21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.38</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.39</v>
       </c>
-      <c r="K21" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.51</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="P21" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="S21" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="T21" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="U21" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="V21" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounting </t>
+          <t xml:space="preserve">Marketing </t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27970</v>
+        <v>25160</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="G22" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="H22" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="I22" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="K22" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="L22" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="M22" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="O22" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P22" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="S22" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="T22" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="U22" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="V22" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Management and Adminstration </t>
+          <t xml:space="preserve">Finance </t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39440</v>
+        <v>20900</v>
       </c>
       <c r="C23" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="D23" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T23" t="n">
         <v>0.43</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>0.28</v>
       </c>
-      <c r="U23" t="n">
-        <v>0.18</v>
-      </c>
       <c r="V23" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marketing </t>
+          <t xml:space="preserve">Other Business Degrees </t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25160</v>
+        <v>26800</v>
       </c>
       <c r="C24" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.63</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="F24" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="G24" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H24" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="I24" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="J24" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="K24" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="L24" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="M24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.23</v>
-      </c>
       <c r="V24" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance </t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>20900</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.28</v>
-      </c>
+          <t xml:space="preserve">Education Degrees </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Business Degrees </t>
+          <t>General Education</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26800</v>
+        <v>27440</v>
       </c>
       <c r="C26" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="E26" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="F26" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T26" t="n">
         <v>0.53</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.41</v>
-      </c>
       <c r="U26" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Degrees </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+          <t>Elementary Education</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>22660</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>General Education</t>
+          <t>Other Education Degrees</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27440</v>
+        <v>28800</v>
       </c>
       <c r="C28" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
         <v>0.49</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="G28" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="H28" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="I28" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="J28" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="K28" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="L28" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="O28" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="P28" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="R28" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="T28" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="U28" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="V28" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Elementary Education</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>22660</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.26</v>
-      </c>
+          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other Education Degrees</t>
+          <t xml:space="preserve">Communications </t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28800</v>
+        <v>24120</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="E30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.49</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="S30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.47</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.38</v>
-      </c>
       <c r="U30" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="V30" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+          <t xml:space="preserve">English Language and Literature </t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>20970</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communications </t>
+          <t xml:space="preserve">Liberal Arts </t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24120</v>
+        <v>13350</v>
       </c>
       <c r="C32" t="n">
-        <v>0.66</v>
+        <v>1.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.66</v>
+        <v>1.2</v>
       </c>
       <c r="E32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L32" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="M32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U32" t="n">
         <v>0.46</v>
       </c>
-      <c r="I32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.28</v>
-      </c>
       <c r="V32" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">English Language and Literature </t>
+          <t xml:space="preserve">History </t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20970</v>
+        <v>21500</v>
       </c>
       <c r="C33" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.61</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.57</v>
-      </c>
       <c r="H33" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I33" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J33" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K33" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M33" t="n">
         <v>0.35</v>
       </c>
-      <c r="L33" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.24</v>
-      </c>
       <c r="N33" t="n">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="O33" t="n">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="P33" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="R33" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="S33" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="T33" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="U33" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="V33" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liberal Arts </t>
+          <t xml:space="preserve">Fine Arts </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13350</v>
+        <v>16660</v>
       </c>
       <c r="C34" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="E34" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="G34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1.02</v>
+        <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="J34" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="K34" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="L34" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="M34" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="N34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T34" t="n">
         <v>0.87</v>
       </c>
-      <c r="O34" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.79</v>
-      </c>
       <c r="U34" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="V34" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">History </t>
+          <t xml:space="preserve">Commerical Art and Graphic Design </t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21500</v>
+        <v>17110</v>
       </c>
       <c r="C35" t="n">
-        <v>0.72</v>
+        <v>1.06</v>
       </c>
       <c r="D35" t="n">
-        <v>0.72</v>
+        <v>1.06</v>
       </c>
       <c r="E35" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="F35" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="G35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O35" t="n">
         <v>0.61</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.82</v>
-      </c>
       <c r="P35" t="n">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="R35" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="S35" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="T35" t="n">
-        <v>0.45</v>
+        <v>0.83</v>
       </c>
       <c r="U35" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="V35" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fine Arts </t>
+          <t xml:space="preserve">Family and Consumer Sciences </t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16660</v>
+        <v>11120</v>
       </c>
       <c r="C36" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="D36" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="E36" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="F36" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="H36" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="J36" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="K36" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="L36" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M36" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="O36" t="n">
-        <v>0.76</v>
+        <v>1.07</v>
       </c>
       <c r="P36" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="S36" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="U36" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commerical Art and Graphic Design </t>
+          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17110</v>
+        <v>18150</v>
       </c>
       <c r="C37" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="D37" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="E37" t="n">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
       <c r="F37" t="n">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="G37" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H37" t="n">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="I37" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="J37" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="K37" t="n">
-        <v>0.62</v>
+        <v>0.35</v>
       </c>
       <c r="L37" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="N37" t="n">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="O37" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="P37" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.22</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.33</v>
-      </c>
       <c r="T37" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="U37" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="V37" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family and Consumer Sciences </t>
+          <t>Criminal Justice and Fire Protection</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11120</v>
+        <v>24310</v>
       </c>
       <c r="C38" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D38" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E38" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="F38" t="n">
-        <v>1.15</v>
+        <v>0.74</v>
       </c>
       <c r="G38" t="n">
-        <v>1.04</v>
+        <v>0.62</v>
       </c>
       <c r="H38" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="I38" t="n">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="K38" t="n">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="L38" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="N38" t="n">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="O38" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="P38" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="R38" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="S38" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="T38" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="U38" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="V38" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
+          <t xml:space="preserve">Social Work </t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18150</v>
+        <v>14320</v>
       </c>
       <c r="C39" t="n">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="F39" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="G39" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H39" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="K39" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="M39" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="O39" t="n">
-        <v>0.82</v>
+        <v>1.18</v>
       </c>
       <c r="P39" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0.67</v>
+        <v>0.97</v>
       </c>
       <c r="S39" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="T39" t="n">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="U39" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="V39" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Criminal Justice and Fire Protection</t>
+          <t xml:space="preserve">Other Degrees </t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24310</v>
+        <v>50010</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="E40" t="n">
-        <v>0.84</v>
+        <v>0.35</v>
       </c>
       <c r="F40" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="G40" t="n">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
       <c r="H40" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="J40" t="n">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
       <c r="K40" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="M40" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0.66</v>
+        <v>0.35</v>
       </c>
       <c r="O40" t="n">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="P40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.54</v>
-      </c>
       <c r="S40" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="T40" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="U40" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="V40" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Social Work </t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>14320</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.53</v>
-      </c>
+          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Degrees </t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>50010</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.19</v>
-      </c>
+          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+          <t>Note: 1. Science and Engineering related fields are included within the "other science and engineering degrees" category.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -6223,62 +5959,6 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Note: 1. Science and Engineering related fields are included within the "other science and engineering degrees" category.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
